--- a/Iowahall.xlsx
+++ b/Iowahall.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="839">
   <si>
     <t>First</t>
   </si>
@@ -2538,6 +2538,9 @@
   </si>
   <si>
     <t>Stufflebeem, Sr.</t>
+  </si>
+  <si>
+    <t>Olson  (deceased)</t>
   </si>
 </sst>
 </file>
@@ -2981,7 +2984,7 @@
         <v>710</v>
       </c>
       <c r="C2" t="str">
-        <f t="shared" ref="C2:C34" si="0">A2&amp;" "&amp;B2</f>
+        <f>A2&amp;" "&amp;B2</f>
         <v>Roger  Aceto (deceased)</v>
       </c>
       <c r="D2">
@@ -3002,7 +3005,7 @@
         <v>646</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" si="0"/>
+        <f>A3&amp;" "&amp;B3</f>
         <v>Gary Alberhasky</v>
       </c>
       <c r="D3">
@@ -3029,7 +3032,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
+        <f>A4&amp;" "&amp;B4</f>
         <v>Ron Amick</v>
       </c>
       <c r="D4">
@@ -3053,7 +3056,7 @@
         <v>761</v>
       </c>
       <c r="C5" t="str">
-        <f t="shared" si="0"/>
+        <f>A5&amp;" "&amp;B5</f>
         <v>John Amsbaugh</v>
       </c>
       <c r="D5">
@@ -3075,7 +3078,7 @@
         <v>767</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" si="0"/>
+        <f>A6&amp;" "&amp;B6</f>
         <v>Steve Anderson</v>
       </c>
       <c r="D6">
@@ -3095,7 +3098,7 @@
         <v>416</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" si="0"/>
+        <f>A7&amp;" "&amp;B7</f>
         <v>Ev Andrew (deceased)</v>
       </c>
       <c r="D7">
@@ -3113,7 +3116,7 @@
         <v>416</v>
       </c>
       <c r="C8" t="str">
-        <f t="shared" si="0"/>
+        <f>A8&amp;" "&amp;B8</f>
         <v>Steve  Andrew (deceased)</v>
       </c>
       <c r="D8">
@@ -3134,7 +3137,7 @@
         <v>713</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="0"/>
+        <f>A9&amp;" "&amp;B9</f>
         <v>Gary Bachus</v>
       </c>
       <c r="D9">
@@ -3152,7 +3155,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="0"/>
+        <f>A10&amp;" "&amp;B10</f>
         <v>Don  Bailey</v>
       </c>
       <c r="D10">
@@ -3173,7 +3176,7 @@
         <v>830</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" ref="C11" si="1">A11&amp;" "&amp;B11</f>
+        <f>A11&amp;" "&amp;B11</f>
         <v>Gordy Baker</v>
       </c>
       <c r="D11">
@@ -3195,7 +3198,7 @@
         <v>481</v>
       </c>
       <c r="C12" t="str">
-        <f t="shared" si="0"/>
+        <f>A12&amp;" "&amp;B12</f>
         <v>Tom Bakey</v>
       </c>
       <c r="D12">
@@ -3219,7 +3222,7 @@
         <v>481</v>
       </c>
       <c r="C13" t="str">
-        <f t="shared" si="0"/>
+        <f>A13&amp;" "&amp;B13</f>
         <v>Dave Bakey</v>
       </c>
       <c r="D13">
@@ -3246,7 +3249,7 @@
         <v>392</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" si="0"/>
+        <f>A14&amp;" "&amp;B14</f>
         <v>Ed Bartlett (deceased)</v>
       </c>
       <c r="D14">
@@ -3264,7 +3267,7 @@
         <v>26</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" si="0"/>
+        <f>A15&amp;" "&amp;B15</f>
         <v>Kenny  Berg</v>
       </c>
       <c r="D15">
@@ -3285,7 +3288,7 @@
         <v>587</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="0"/>
+        <f>A16&amp;" "&amp;B16</f>
         <v>Bob Best (deceased)</v>
       </c>
       <c r="D16">
@@ -3312,7 +3315,7 @@
         <v>552</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" si="0"/>
+        <f>A17&amp;" "&amp;B17</f>
         <v>Wendell  Blankenburg</v>
       </c>
       <c r="D17">
@@ -3336,7 +3339,7 @@
         <v>770</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" si="0"/>
+        <f>A18&amp;" "&amp;B18</f>
         <v>Keith Boots</v>
       </c>
       <c r="D18">
@@ -3358,7 +3361,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="0"/>
+        <f>A19&amp;" "&amp;B19</f>
         <v>Gregg Bosch</v>
       </c>
       <c r="D19">
@@ -3382,7 +3385,7 @@
         <v>818</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="0"/>
+        <f>A20&amp;" "&amp;B20</f>
         <v>Mel  Bowen (deceased)</v>
       </c>
       <c r="D20">
@@ -3403,7 +3406,7 @@
         <v>716</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" si="0"/>
+        <f>A21&amp;" "&amp;B21</f>
         <v>Dodge Brad</v>
       </c>
       <c r="D21">
@@ -3421,7 +3424,7 @@
         <v>775</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" si="0"/>
+        <f>A22&amp;" "&amp;B22</f>
         <v>Bob Brady</v>
       </c>
       <c r="D22">
@@ -3443,7 +3446,7 @@
         <v>447</v>
       </c>
       <c r="C23" t="str">
-        <f t="shared" si="0"/>
+        <f>A23&amp;" "&amp;B23</f>
         <v>Clark  Brollier (deceased)</v>
       </c>
       <c r="D23">
@@ -3461,7 +3464,7 @@
         <v>411</v>
       </c>
       <c r="C24" t="str">
-        <f t="shared" si="0"/>
+        <f>A24&amp;" "&amp;B24</f>
         <v>Walter Broussard (deceased)</v>
       </c>
       <c r="D24">
@@ -3479,7 +3482,7 @@
         <v>383</v>
       </c>
       <c r="C25" t="str">
-        <f t="shared" si="0"/>
+        <f>A25&amp;" "&amp;B25</f>
         <v>Roger  Buddin</v>
       </c>
       <c r="D25">
@@ -3509,7 +3512,7 @@
         <v>460</v>
       </c>
       <c r="C26" t="str">
-        <f t="shared" si="0"/>
+        <f>A26&amp;" "&amp;B26</f>
         <v>Ray  Burlinghame (deceased)</v>
       </c>
       <c r="D26">
@@ -3528,7 +3531,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="str">
-        <f t="shared" si="0"/>
+        <f>A27&amp;" "&amp;B27</f>
         <v>Paul  Burnett</v>
       </c>
       <c r="D27">
@@ -3549,7 +3552,7 @@
         <v>589</v>
       </c>
       <c r="C28" t="str">
-        <f t="shared" si="0"/>
+        <f>A28&amp;" "&amp;B28</f>
         <v>Tom  Busch (deceased 2006)</v>
       </c>
       <c r="D28">
@@ -3570,7 +3573,7 @@
         <v>46</v>
       </c>
       <c r="C29" t="str">
-        <f t="shared" si="0"/>
+        <f>A29&amp;" "&amp;B29</f>
         <v>Steve  Calvert</v>
       </c>
       <c r="D29">
@@ -3591,7 +3594,7 @@
         <v>591</v>
       </c>
       <c r="C30" t="str">
-        <f t="shared" si="0"/>
+        <f>A30&amp;" "&amp;B30</f>
         <v>Pete Canakes</v>
       </c>
       <c r="D30">
@@ -3609,7 +3612,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="str">
-        <f t="shared" si="0"/>
+        <f>A31&amp;" "&amp;B31</f>
         <v>Don  Carlson</v>
       </c>
       <c r="D31">
@@ -3630,7 +3633,7 @@
         <v>561</v>
       </c>
       <c r="C32" t="str">
-        <f t="shared" si="0"/>
+        <f>A32&amp;" "&amp;B32</f>
         <v>LeRoy Carlson (deceased)</v>
       </c>
       <c r="D32">
@@ -3648,7 +3651,7 @@
         <v>408</v>
       </c>
       <c r="C33" t="str">
-        <f t="shared" si="0"/>
+        <f>A33&amp;" "&amp;B33</f>
         <v>Al Carr (deceased)</v>
       </c>
       <c r="D33">
@@ -3666,7 +3669,7 @@
         <v>824</v>
       </c>
       <c r="C34" t="str">
-        <f t="shared" si="0"/>
+        <f>A34&amp;" "&amp;B34</f>
         <v>Jim  Caviness (deceased)</v>
       </c>
       <c r="D34">
@@ -3687,7 +3690,7 @@
         <v>780</v>
       </c>
       <c r="C35" t="str">
-        <f t="shared" ref="C35:C67" si="2">A35&amp;" "&amp;B35</f>
+        <f>A35&amp;" "&amp;B35</f>
         <v>Lawrence Cheyne  (deceased)</v>
       </c>
       <c r="D35">
@@ -3705,7 +3708,7 @@
         <v>54</v>
       </c>
       <c r="C36" t="str">
-        <f t="shared" si="2"/>
+        <f>A36&amp;" "&amp;B36</f>
         <v>Gary  Christensen</v>
       </c>
       <c r="D36">
@@ -3726,7 +3729,7 @@
         <v>54</v>
       </c>
       <c r="C37" t="str">
-        <f t="shared" si="2"/>
+        <f>A37&amp;" "&amp;B37</f>
         <v>Cory Christensen</v>
       </c>
       <c r="D37">
@@ -3747,7 +3750,7 @@
         <v>696</v>
       </c>
       <c r="C38" t="str">
-        <f t="shared" si="2"/>
+        <f>A38&amp;" "&amp;B38</f>
         <v>Mike Christner</v>
       </c>
       <c r="D38">
@@ -3765,7 +3768,7 @@
         <v>636</v>
       </c>
       <c r="C39" t="str">
-        <f t="shared" si="2"/>
+        <f>A39&amp;" "&amp;B39</f>
         <v>Jim Ciesielski (deceased)</v>
       </c>
       <c r="D39">
@@ -3792,7 +3795,7 @@
         <v>782</v>
       </c>
       <c r="C40" t="str">
-        <f t="shared" si="2"/>
+        <f>A40&amp;" "&amp;B40</f>
         <v>Mike Clark</v>
       </c>
       <c r="D40">
@@ -3816,7 +3819,7 @@
         <v>728</v>
       </c>
       <c r="C41" t="str">
-        <f t="shared" si="2"/>
+        <f>A41&amp;" "&amp;B41</f>
         <v>Bill Clark (deceased)</v>
       </c>
       <c r="D41">
@@ -3834,7 +3837,7 @@
         <v>63</v>
       </c>
       <c r="C42" t="str">
-        <f t="shared" si="2"/>
+        <f>A42&amp;" "&amp;B42</f>
         <v xml:space="preserve">Edward  Colbert </v>
       </c>
       <c r="D42">
@@ -3855,7 +3858,7 @@
         <v>67</v>
       </c>
       <c r="C43" t="str">
-        <f t="shared" si="2"/>
+        <f>A43&amp;" "&amp;B43</f>
         <v xml:space="preserve">Jay Coleman </v>
       </c>
       <c r="D43">
@@ -3873,7 +3876,7 @@
         <v>442</v>
       </c>
       <c r="C44" t="str">
-        <f t="shared" si="2"/>
+        <f>A44&amp;" "&amp;B44</f>
         <v>Sam Cordaro (deceased)</v>
       </c>
       <c r="D44">
@@ -3891,7 +3894,7 @@
         <v>643</v>
       </c>
       <c r="C45" t="str">
-        <f t="shared" si="2"/>
+        <f>A45&amp;" "&amp;B45</f>
         <v>Tarry Cory</v>
       </c>
       <c r="D45">
@@ -3915,7 +3918,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="str">
-        <f t="shared" si="2"/>
+        <f>A46&amp;" "&amp;B46</f>
         <v>Bob  Daniels</v>
       </c>
       <c r="D46">
@@ -3936,7 +3939,7 @@
         <v>69</v>
       </c>
       <c r="C47" t="str">
-        <f t="shared" si="2"/>
+        <f>A47&amp;" "&amp;B47</f>
         <v>Rick Daniels</v>
       </c>
       <c r="D47">
@@ -3954,7 +3957,7 @@
         <v>386</v>
       </c>
       <c r="C48" t="str">
-        <f t="shared" si="2"/>
+        <f>A48&amp;" "&amp;B48</f>
         <v>Don  Dannen (deceased)</v>
       </c>
       <c r="D48">
@@ -3972,7 +3975,7 @@
         <v>730</v>
       </c>
       <c r="C49" t="str">
-        <f t="shared" si="2"/>
+        <f>A49&amp;" "&amp;B49</f>
         <v>Jason Darling</v>
       </c>
       <c r="D49">
@@ -3999,7 +4002,7 @@
         <v>730</v>
       </c>
       <c r="C50" t="str">
-        <f t="shared" si="2"/>
+        <f>A50&amp;" "&amp;B50</f>
         <v>Matt Darling</v>
       </c>
       <c r="D50">
@@ -4026,7 +4029,7 @@
         <v>452</v>
       </c>
       <c r="C51" t="str">
-        <f t="shared" si="2"/>
+        <f>A51&amp;" "&amp;B51</f>
         <v>Nyall Davis (deceased)</v>
       </c>
       <c r="D51">
@@ -4044,7 +4047,7 @@
         <v>452</v>
       </c>
       <c r="C52" t="str">
-        <f t="shared" si="2"/>
+        <f>A52&amp;" "&amp;B52</f>
         <v>Abie Davis (deceased)</v>
       </c>
       <c r="D52">
@@ -4062,7 +4065,7 @@
         <v>473</v>
       </c>
       <c r="C53" t="str">
-        <f t="shared" si="2"/>
+        <f>A53&amp;" "&amp;B53</f>
         <v>Don  Deberg</v>
       </c>
       <c r="D53">
@@ -4083,7 +4086,7 @@
         <v>74</v>
       </c>
       <c r="C54" t="str">
-        <f t="shared" si="2"/>
+        <f>A54&amp;" "&amp;B54</f>
         <v xml:space="preserve">Jack  Delbridge </v>
       </c>
       <c r="D54">
@@ -4104,7 +4107,7 @@
         <v>697</v>
       </c>
       <c r="C55" t="str">
-        <f t="shared" si="2"/>
+        <f>A55&amp;" "&amp;B55</f>
         <v>Denny Delorit</v>
       </c>
       <c r="D55">
@@ -4122,7 +4125,7 @@
         <v>459</v>
       </c>
       <c r="C56" t="str">
-        <f t="shared" si="2"/>
+        <f>A56&amp;" "&amp;B56</f>
         <v>LeRoy Dimon (deceased)</v>
       </c>
       <c r="D56">
@@ -4140,7 +4143,7 @@
         <v>612</v>
       </c>
       <c r="C57" t="str">
-        <f t="shared" ref="C57" si="3">A57&amp;" "&amp;B57</f>
+        <f>A57&amp;" "&amp;B57</f>
         <v>Dave Donahue</v>
       </c>
       <c r="D57">
@@ -4158,7 +4161,7 @@
         <v>612</v>
       </c>
       <c r="C58" t="str">
-        <f t="shared" si="2"/>
+        <f>A58&amp;" "&amp;B58</f>
         <v>Steve Donahue</v>
       </c>
       <c r="D58">
@@ -4176,7 +4179,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="str">
-        <f t="shared" si="2"/>
+        <f>A59&amp;" "&amp;B59</f>
         <v xml:space="preserve">Lance  Dreesman </v>
       </c>
       <c r="D59">
@@ -4197,7 +4200,7 @@
         <v>82</v>
       </c>
       <c r="C60" t="str">
-        <f t="shared" si="2"/>
+        <f>A60&amp;" "&amp;B60</f>
         <v xml:space="preserve">Bill  Driscoll </v>
       </c>
       <c r="D60">
@@ -4218,7 +4221,7 @@
         <v>718</v>
       </c>
       <c r="C61" t="str">
-        <f t="shared" si="2"/>
+        <f>A61&amp;" "&amp;B61</f>
         <v>Darren Dubsky</v>
       </c>
       <c r="D61">
@@ -4236,7 +4239,7 @@
         <v>439</v>
       </c>
       <c r="C62" t="str">
-        <f t="shared" si="2"/>
+        <f>A62&amp;" "&amp;B62</f>
         <v>Lou Dvorak (deceased)</v>
       </c>
       <c r="D62">
@@ -4254,7 +4257,7 @@
         <v>85</v>
       </c>
       <c r="C63" t="str">
-        <f t="shared" si="2"/>
+        <f>A63&amp;" "&amp;B63</f>
         <v xml:space="preserve">Ben  Edwards </v>
       </c>
       <c r="D63">
@@ -4275,7 +4278,7 @@
         <v>89</v>
       </c>
       <c r="C64" t="str">
-        <f t="shared" si="2"/>
+        <f>A64&amp;" "&amp;B64</f>
         <v xml:space="preserve">John  Ege </v>
       </c>
       <c r="D64">
@@ -4296,7 +4299,7 @@
         <v>89</v>
       </c>
       <c r="C65" t="str">
-        <f t="shared" si="2"/>
+        <f>A65&amp;" "&amp;B65</f>
         <v xml:space="preserve">Ron Ege </v>
       </c>
       <c r="D65">
@@ -4318,7 +4321,7 @@
         <v>472</v>
       </c>
       <c r="C66" t="str">
-        <f t="shared" si="2"/>
+        <f>A66&amp;" "&amp;B66</f>
         <v>Ken  Elkema  (deceased)</v>
       </c>
       <c r="D66">
@@ -4336,7 +4339,7 @@
         <v>93</v>
       </c>
       <c r="C67" t="str">
-        <f t="shared" si="2"/>
+        <f>A67&amp;" "&amp;B67</f>
         <v xml:space="preserve">Bob  Elliott </v>
       </c>
       <c r="D67">
@@ -4357,7 +4360,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="str">
-        <f t="shared" ref="C68:C99" si="4">A68&amp;" "&amp;B68</f>
+        <f>A68&amp;" "&amp;B68</f>
         <v xml:space="preserve">Cal  Ernst </v>
       </c>
       <c r="D68">
@@ -4378,7 +4381,7 @@
         <v>437</v>
       </c>
       <c r="C69" t="str">
-        <f t="shared" si="4"/>
+        <f>A69&amp;" "&amp;B69</f>
         <v>Floyd "Cocky" Espinosa  (deceased)</v>
       </c>
       <c r="D69">
@@ -4396,7 +4399,7 @@
         <v>437</v>
       </c>
       <c r="C70" t="str">
-        <f t="shared" si="4"/>
+        <f>A70&amp;" "&amp;B70</f>
         <v>Paul  Espinosa  (deceased)</v>
       </c>
       <c r="D70">
@@ -4414,7 +4417,7 @@
         <v>613</v>
       </c>
       <c r="C71" t="str">
-        <f t="shared" si="4"/>
+        <f>A71&amp;" "&amp;B71</f>
         <v>Steve Fagan</v>
       </c>
       <c r="D71">
@@ -4432,7 +4435,7 @@
         <v>100</v>
       </c>
       <c r="C72" t="str">
-        <f t="shared" si="4"/>
+        <f>A72&amp;" "&amp;B72</f>
         <v xml:space="preserve">L.J.  Favors </v>
       </c>
       <c r="D72">
@@ -4453,7 +4456,7 @@
         <v>470</v>
       </c>
       <c r="C73" t="str">
-        <f t="shared" si="4"/>
+        <f>A73&amp;" "&amp;B73</f>
         <v>Denny Ferch (deceased 1999)</v>
       </c>
       <c r="D73">
@@ -4471,7 +4474,7 @@
         <v>445</v>
       </c>
       <c r="C74" t="str">
-        <f t="shared" si="4"/>
+        <f>A74&amp;" "&amp;B74</f>
         <v>Dick  Finn (deceased)</v>
       </c>
       <c r="D74">
@@ -4489,7 +4492,7 @@
         <v>104</v>
       </c>
       <c r="C75" t="str">
-        <f t="shared" si="4"/>
+        <f>A75&amp;" "&amp;B75</f>
         <v xml:space="preserve">Dick  Fisher </v>
       </c>
       <c r="D75">
@@ -4510,7 +4513,7 @@
         <v>104</v>
       </c>
       <c r="C76" t="str">
-        <f t="shared" si="4"/>
+        <f>A76&amp;" "&amp;B76</f>
         <v xml:space="preserve">Rollo  Fisher </v>
       </c>
       <c r="D76">
@@ -4531,7 +4534,7 @@
         <v>104</v>
       </c>
       <c r="C77" t="str">
-        <f t="shared" si="4"/>
+        <f>A77&amp;" "&amp;B77</f>
         <v xml:space="preserve">Wayne  Fisher </v>
       </c>
       <c r="D77">
@@ -4552,7 +4555,7 @@
         <v>114</v>
       </c>
       <c r="C78" t="str">
-        <f t="shared" si="4"/>
+        <f>A78&amp;" "&amp;B78</f>
         <v xml:space="preserve">Patrick  Fleming </v>
       </c>
       <c r="D78" t="s">
@@ -4573,7 +4576,7 @@
         <v>619</v>
       </c>
       <c r="C79" t="str">
-        <f t="shared" si="4"/>
+        <f>A79&amp;" "&amp;B79</f>
         <v>Francis Foley</v>
       </c>
       <c r="D79">
@@ -4591,7 +4594,7 @@
         <v>118</v>
       </c>
       <c r="C80" t="str">
-        <f t="shared" si="4"/>
+        <f>A80&amp;" "&amp;B80</f>
         <v>Bob Fontana</v>
       </c>
       <c r="D80">
@@ -4618,7 +4621,7 @@
         <v>428</v>
       </c>
       <c r="C81" t="str">
-        <f t="shared" si="4"/>
+        <f>A81&amp;" "&amp;B81</f>
         <v>Floyde "Fuji" Foulton (deceased)</v>
       </c>
       <c r="D81">
@@ -4636,7 +4639,7 @@
         <v>814</v>
       </c>
       <c r="C82" t="str">
-        <f t="shared" si="4"/>
+        <f>A82&amp;" "&amp;B82</f>
         <v>Warren Gichard</v>
       </c>
       <c r="D82">
@@ -4657,7 +4660,7 @@
         <v>127</v>
       </c>
       <c r="C83" t="str">
-        <f t="shared" si="4"/>
+        <f>A83&amp;" "&amp;B83</f>
         <v xml:space="preserve">Jim  Gorman  </v>
       </c>
       <c r="D83">
@@ -4678,7 +4681,7 @@
         <v>390</v>
       </c>
       <c r="C84" t="str">
-        <f t="shared" si="4"/>
+        <f>A84&amp;" "&amp;B84</f>
         <v>Arnie Greene (deceased)</v>
       </c>
       <c r="D84">
@@ -4696,7 +4699,7 @@
         <v>799</v>
       </c>
       <c r="C85" t="str">
-        <f t="shared" si="4"/>
+        <f>A85&amp;" "&amp;B85</f>
         <v>Billy Greer</v>
       </c>
       <c r="D85">
@@ -4717,7 +4720,7 @@
         <v>399</v>
       </c>
       <c r="C86" t="str">
-        <f t="shared" si="4"/>
+        <f>A86&amp;" "&amp;B86</f>
         <v>Larry Hagen (deceased)</v>
       </c>
       <c r="D86">
@@ -4735,7 +4738,7 @@
         <v>130</v>
       </c>
       <c r="C87" t="str">
-        <f t="shared" si="4"/>
+        <f>A87&amp;" "&amp;B87</f>
         <v xml:space="preserve">Ray  Hamad </v>
       </c>
       <c r="D87">
@@ -4756,7 +4759,7 @@
         <v>804</v>
       </c>
       <c r="C88" t="str">
-        <f t="shared" si="4"/>
+        <f>A88&amp;" "&amp;B88</f>
         <v>Dave Hammel</v>
       </c>
       <c r="D88">
@@ -4777,7 +4780,7 @@
         <v>124</v>
       </c>
       <c r="C89" t="str">
-        <f t="shared" si="4"/>
+        <f>A89&amp;" "&amp;B89</f>
         <v>Larry (Fuzzy) Hanes</v>
       </c>
       <c r="D89">
@@ -4798,7 +4801,7 @@
         <v>133</v>
       </c>
       <c r="C90" t="str">
-        <f t="shared" si="4"/>
+        <f>A90&amp;" "&amp;B90</f>
         <v xml:space="preserve">Kent  Hansen </v>
       </c>
       <c r="D90">
@@ -4819,7 +4822,7 @@
         <v>519</v>
       </c>
       <c r="C91" t="str">
-        <f t="shared" si="4"/>
+        <f>A91&amp;" "&amp;B91</f>
         <v>Curtis Hanson (deceased)</v>
       </c>
       <c r="D91">
@@ -4837,7 +4840,7 @@
         <v>519</v>
       </c>
       <c r="C92" t="str">
-        <f t="shared" si="4"/>
+        <f>A92&amp;" "&amp;B92</f>
         <v>Gary "Zip" Hanson (deceased)</v>
       </c>
       <c r="D92">
@@ -4855,7 +4858,7 @@
         <v>611</v>
       </c>
       <c r="C93" t="str">
-        <f t="shared" si="4"/>
+        <f>A93&amp;" "&amp;B93</f>
         <v>Kevin Hartwig</v>
       </c>
       <c r="D93">
@@ -4873,7 +4876,7 @@
         <v>624</v>
       </c>
       <c r="C94" t="str">
-        <f t="shared" si="4"/>
+        <f>A94&amp;" "&amp;B94</f>
         <v>Rick Hartzell</v>
       </c>
       <c r="D94">
@@ -4891,7 +4894,7 @@
         <v>663</v>
       </c>
       <c r="C95" t="str">
-        <f t="shared" si="4"/>
+        <f>A95&amp;" "&amp;B95</f>
         <v>Floyd Hazelbaker</v>
       </c>
       <c r="D95">
@@ -4909,7 +4912,7 @@
         <v>498</v>
       </c>
       <c r="C96" t="str">
-        <f t="shared" si="4"/>
+        <f>A96&amp;" "&amp;B96</f>
         <v>Dave Hearn</v>
       </c>
       <c r="D96">
@@ -4933,7 +4936,7 @@
         <v>136</v>
       </c>
       <c r="C97" t="str">
-        <f t="shared" si="4"/>
+        <f>A97&amp;" "&amp;B97</f>
         <v xml:space="preserve">Bill  Helling </v>
       </c>
       <c r="D97">
@@ -4954,7 +4957,7 @@
         <v>616</v>
       </c>
       <c r="C98" t="str">
-        <f t="shared" si="4"/>
+        <f>A98&amp;" "&amp;B98</f>
         <v xml:space="preserve">Larry Hendricks (deceased) </v>
       </c>
       <c r="D98">
@@ -4972,7 +4975,7 @@
         <v>633</v>
       </c>
       <c r="C99" t="str">
-        <f t="shared" si="4"/>
+        <f>A99&amp;" "&amp;B99</f>
         <v>Don  Hensley (deceased)</v>
       </c>
       <c r="D99">
@@ -4993,7 +4996,7 @@
         <v>821</v>
       </c>
       <c r="C100" t="str">
-        <f t="shared" ref="C100" si="5">A100&amp;" "&amp;B100</f>
+        <f>A100&amp;" "&amp;B100</f>
         <v>Willie Herndon (deceased)</v>
       </c>
       <c r="D100">
@@ -5043,7 +5046,7 @@
         <v>568</v>
       </c>
       <c r="C102" t="str">
-        <f t="shared" ref="C102:C133" si="6">A102&amp;" "&amp;B102</f>
+        <f>A102&amp;" "&amp;B102</f>
         <v>Bob Hoskins (deceased)</v>
       </c>
       <c r="D102">
@@ -5073,7 +5076,7 @@
         <v>146</v>
       </c>
       <c r="C103" t="str">
-        <f t="shared" si="6"/>
+        <f>A103&amp;" "&amp;B103</f>
         <v xml:space="preserve">Bruce  Hotchkiss </v>
       </c>
       <c r="D103">
@@ -5094,7 +5097,7 @@
         <v>801</v>
       </c>
       <c r="C104" t="str">
-        <f t="shared" si="6"/>
+        <f>A104&amp;" "&amp;B104</f>
         <v>Bob Howard</v>
       </c>
       <c r="D104">
@@ -5115,7 +5118,7 @@
         <v>150</v>
       </c>
       <c r="C105" t="str">
-        <f t="shared" si="6"/>
+        <f>A105&amp;" "&amp;B105</f>
         <v xml:space="preserve">Fred  Jackson </v>
       </c>
       <c r="D105">
@@ -5136,7 +5139,7 @@
         <v>419</v>
       </c>
       <c r="C106" t="str">
-        <f t="shared" si="6"/>
+        <f>A106&amp;" "&amp;B106</f>
         <v>Earl "Huck" Jackson  (deceased)</v>
       </c>
       <c r="D106">
@@ -5154,7 +5157,7 @@
         <v>714</v>
       </c>
       <c r="C107" t="str">
-        <f t="shared" si="6"/>
+        <f>A107&amp;" "&amp;B107</f>
         <v>Blake James</v>
       </c>
       <c r="D107">
@@ -5172,7 +5175,7 @@
         <v>689</v>
       </c>
       <c r="C108" t="str">
-        <f t="shared" si="6"/>
+        <f>A108&amp;" "&amp;B108</f>
         <v>Dale  Johansen (deceased)</v>
       </c>
       <c r="D108">
@@ -5193,7 +5196,7 @@
         <v>457</v>
       </c>
       <c r="C109" t="str">
-        <f t="shared" si="6"/>
+        <f>A109&amp;" "&amp;B109</f>
         <v>Bob Johns (deceased)</v>
       </c>
       <c r="D109">
@@ -5211,7 +5214,7 @@
         <v>393</v>
       </c>
       <c r="C110" t="str">
-        <f t="shared" si="6"/>
+        <f>A110&amp;" "&amp;B110</f>
         <v>Dale  Johnson (deceased)</v>
       </c>
       <c r="D110">
@@ -5229,7 +5232,7 @@
         <v>413</v>
       </c>
       <c r="C111" t="str">
-        <f t="shared" si="6"/>
+        <f>A111&amp;" "&amp;B111</f>
         <v>Dick  Jones (deceased)</v>
       </c>
       <c r="D111">
@@ -5247,7 +5250,7 @@
         <v>413</v>
       </c>
       <c r="C112" t="str">
-        <f t="shared" si="6"/>
+        <f>A112&amp;" "&amp;B112</f>
         <v>Bill Jones (deceased)</v>
       </c>
       <c r="D112">
@@ -5265,7 +5268,7 @@
         <v>444</v>
       </c>
       <c r="C113" t="str">
-        <f t="shared" si="6"/>
+        <f>A113&amp;" "&amp;B113</f>
         <v>Howard  Judd (deceased)</v>
       </c>
       <c r="D113">
@@ -5283,7 +5286,7 @@
         <v>711</v>
       </c>
       <c r="C114" t="str">
-        <f t="shared" si="6"/>
+        <f>A114&amp;" "&amp;B114</f>
         <v>Vic  Kadlec  (deceased)</v>
       </c>
       <c r="D114">
@@ -5304,7 +5307,7 @@
         <v>159</v>
       </c>
       <c r="C115" t="str">
-        <f t="shared" si="6"/>
+        <f>A115&amp;" "&amp;B115</f>
         <v>Ronald  Kain</v>
       </c>
       <c r="D115">
@@ -5325,7 +5328,7 @@
         <v>539</v>
       </c>
       <c r="C116" t="str">
-        <f t="shared" si="6"/>
+        <f>A116&amp;" "&amp;B116</f>
         <v>Steve Kaiser</v>
       </c>
       <c r="D116">
@@ -5346,7 +5349,7 @@
         <v>671</v>
       </c>
       <c r="C117" t="str">
-        <f t="shared" si="6"/>
+        <f>A117&amp;" "&amp;B117</f>
         <v>Sonny Kalishek</v>
       </c>
       <c r="D117">
@@ -5373,7 +5376,7 @@
         <v>688</v>
       </c>
       <c r="C118" t="str">
-        <f t="shared" si="6"/>
+        <f>A118&amp;" "&amp;B118</f>
         <v>Irv  Kawarsky (deceased)</v>
       </c>
       <c r="D118">
@@ -5394,7 +5397,7 @@
         <v>166</v>
       </c>
       <c r="C119" t="str">
-        <f t="shared" si="6"/>
+        <f>A119&amp;" "&amp;B119</f>
         <v xml:space="preserve">Bobby  Keefer </v>
       </c>
       <c r="D119">
@@ -5415,7 +5418,7 @@
         <v>170</v>
       </c>
       <c r="C120" t="str">
-        <f t="shared" si="6"/>
+        <f>A120&amp;" "&amp;B120</f>
         <v>John Kelly</v>
       </c>
       <c r="D120">
@@ -5445,7 +5448,7 @@
         <v>625</v>
       </c>
       <c r="C121" t="str">
-        <f t="shared" si="6"/>
+        <f>A121&amp;" "&amp;B121</f>
         <v>Steve Kerian</v>
       </c>
       <c r="D121">
@@ -5463,7 +5466,7 @@
         <v>660</v>
       </c>
       <c r="C122" t="str">
-        <f t="shared" si="6"/>
+        <f>A122&amp;" "&amp;B122</f>
         <v>Dick  Kerker (deceased)</v>
       </c>
       <c r="D122">
@@ -5484,7 +5487,7 @@
         <v>407</v>
       </c>
       <c r="C123" t="str">
-        <f t="shared" si="6"/>
+        <f>A123&amp;" "&amp;B123</f>
         <v>Frank V. "Chuck" Klein (deceased)</v>
       </c>
       <c r="D123">
@@ -5502,7 +5505,7 @@
         <v>179</v>
       </c>
       <c r="C124" t="str">
-        <f t="shared" si="6"/>
+        <f>A124&amp;" "&amp;B124</f>
         <v>Gene Knop</v>
       </c>
       <c r="D124">
@@ -5529,7 +5532,7 @@
         <v>778</v>
       </c>
       <c r="C125" t="str">
-        <f t="shared" si="6"/>
+        <f>A125&amp;" "&amp;B125</f>
         <v>Robert  W. Kramer (deceased)</v>
       </c>
       <c r="D125">
@@ -5550,7 +5553,7 @@
         <v>526</v>
       </c>
       <c r="C126" t="str">
-        <f t="shared" si="6"/>
+        <f>A126&amp;" "&amp;B126</f>
         <v>Rick Kriz</v>
       </c>
       <c r="D126">
@@ -5568,7 +5571,7 @@
         <v>461</v>
       </c>
       <c r="C127" t="str">
-        <f t="shared" si="6"/>
+        <f>A127&amp;" "&amp;B127</f>
         <v>Don  Kruse (deceased)</v>
       </c>
       <c r="D127">
@@ -5586,7 +5589,7 @@
         <v>779</v>
       </c>
       <c r="C128" t="str">
-        <f t="shared" si="6"/>
+        <f>A128&amp;" "&amp;B128</f>
         <v>Walter "Sonny"  Kull  (deceased)</v>
       </c>
       <c r="D128">
@@ -5607,7 +5610,7 @@
         <v>186</v>
       </c>
       <c r="C129" t="str">
-        <f t="shared" si="6"/>
+        <f>A129&amp;" "&amp;B129</f>
         <v xml:space="preserve">Gale  Kurtz </v>
       </c>
       <c r="D129">
@@ -5628,7 +5631,7 @@
         <v>435</v>
       </c>
       <c r="C130" t="str">
-        <f t="shared" si="6"/>
+        <f>A130&amp;" "&amp;B130</f>
         <v>Hank Landgren (deceased)</v>
       </c>
       <c r="D130">
@@ -5646,7 +5649,7 @@
         <v>769</v>
       </c>
       <c r="C131" t="str">
-        <f t="shared" si="6"/>
+        <f>A131&amp;" "&amp;B131</f>
         <v>Jack  Larson</v>
       </c>
       <c r="D131">
@@ -5666,7 +5669,7 @@
         <v>740</v>
       </c>
       <c r="C132" t="str">
-        <f t="shared" si="6"/>
+        <f>A132&amp;" "&amp;B132</f>
         <v>Dale  Lassen</v>
       </c>
       <c r="D132">
@@ -5694,7 +5697,7 @@
         <v>602</v>
       </c>
       <c r="C133" t="str">
-        <f t="shared" si="6"/>
+        <f>A133&amp;" "&amp;B133</f>
         <v xml:space="preserve">Les  Lawrence </v>
       </c>
       <c r="D133">
@@ -5715,7 +5718,7 @@
         <v>192</v>
       </c>
       <c r="C134" t="str">
-        <f t="shared" ref="C134:C165" si="7">A134&amp;" "&amp;B134</f>
+        <f>A134&amp;" "&amp;B134</f>
         <v>Doug Lindaman</v>
       </c>
       <c r="D134">
@@ -5748,7 +5751,7 @@
         <v>468</v>
       </c>
       <c r="C135" t="str">
-        <f t="shared" si="7"/>
+        <f>A135&amp;" "&amp;B135</f>
         <v>Franz Linden (deceased)</v>
       </c>
       <c r="D135">
@@ -5769,7 +5772,7 @@
         <v>203</v>
       </c>
       <c r="C136" t="str">
-        <f t="shared" si="7"/>
+        <f>A136&amp;" "&amp;B136</f>
         <v xml:space="preserve">Dennis  Linderbaum </v>
       </c>
       <c r="D136">
@@ -5799,7 +5802,7 @@
         <v>403</v>
       </c>
       <c r="C137" t="str">
-        <f t="shared" si="7"/>
+        <f>A137&amp;" "&amp;B137</f>
         <v>Everett Long (deceased)</v>
       </c>
       <c r="D137">
@@ -5818,7 +5821,7 @@
         <v>403</v>
       </c>
       <c r="C138" t="str">
-        <f t="shared" si="7"/>
+        <f>A138&amp;" "&amp;B138</f>
         <v>Carl Long (deceased)</v>
       </c>
       <c r="D138">
@@ -5837,7 +5840,7 @@
         <v>207</v>
       </c>
       <c r="C139" t="str">
-        <f t="shared" si="7"/>
+        <f>A139&amp;" "&amp;B139</f>
         <v xml:space="preserve">Gus  Luke </v>
       </c>
       <c r="D139">
@@ -5858,7 +5861,7 @@
         <v>720</v>
       </c>
       <c r="C140" t="str">
-        <f t="shared" si="7"/>
+        <f>A140&amp;" "&amp;B140</f>
         <v>Ron (deceased) Macek</v>
       </c>
       <c r="D140">
@@ -5876,7 +5879,7 @@
         <v>562</v>
       </c>
       <c r="C141" t="str">
-        <f t="shared" si="7"/>
+        <f>A141&amp;" "&amp;B141</f>
         <v>Paul Magan (deceased)</v>
       </c>
       <c r="D141">
@@ -5894,7 +5897,7 @@
         <v>563</v>
       </c>
       <c r="C142" t="str">
-        <f t="shared" si="7"/>
+        <f>A142&amp;" "&amp;B142</f>
         <v>Steve  Maguire (deceased)</v>
       </c>
       <c r="D142">
@@ -5915,7 +5918,7 @@
         <v>443</v>
       </c>
       <c r="C143" t="str">
-        <f t="shared" si="7"/>
+        <f>A143&amp;" "&amp;B143</f>
         <v>Ed Mann (deceased)</v>
       </c>
       <c r="D143">
@@ -5933,7 +5936,7 @@
         <v>722</v>
       </c>
       <c r="C144" t="str">
-        <f t="shared" si="7"/>
+        <f>A144&amp;" "&amp;B144</f>
         <v>Peter Marasco</v>
       </c>
       <c r="D144">
@@ -5951,7 +5954,7 @@
         <v>212</v>
       </c>
       <c r="C145" t="str">
-        <f t="shared" si="7"/>
+        <f>A145&amp;" "&amp;B145</f>
         <v xml:space="preserve">Merle  Marsh </v>
       </c>
       <c r="D145">
@@ -5972,7 +5975,7 @@
         <v>418</v>
       </c>
       <c r="C146" t="str">
-        <f t="shared" si="7"/>
+        <f>A146&amp;" "&amp;B146</f>
         <v>Louie Mays (deceased)</v>
       </c>
       <c r="D146">
@@ -5990,7 +5993,7 @@
         <v>606</v>
       </c>
       <c r="C147" t="str">
-        <f t="shared" si="7"/>
+        <f>A147&amp;" "&amp;B147</f>
         <v>Duke McCullough</v>
       </c>
       <c r="D147">
@@ -6008,7 +6011,7 @@
         <v>215</v>
       </c>
       <c r="C148" t="str">
-        <f t="shared" si="7"/>
+        <f>A148&amp;" "&amp;B148</f>
         <v xml:space="preserve">Jim  McGrew </v>
       </c>
       <c r="D148">
@@ -6029,7 +6032,7 @@
         <v>422</v>
       </c>
       <c r="C149" t="str">
-        <f t="shared" si="7"/>
+        <f>A149&amp;" "&amp;B149</f>
         <v>Bob McLaughlin (deceased)</v>
       </c>
       <c r="D149">
@@ -6047,7 +6050,7 @@
         <v>401</v>
       </c>
       <c r="C150" t="str">
-        <f t="shared" si="7"/>
+        <f>A150&amp;" "&amp;B150</f>
         <v>John Mekshes (deceased)</v>
       </c>
       <c r="D150">
@@ -6065,7 +6068,7 @@
         <v>219</v>
       </c>
       <c r="C151" t="str">
-        <f t="shared" si="7"/>
+        <f>A151&amp;" "&amp;B151</f>
         <v xml:space="preserve">Clark  Menough </v>
       </c>
       <c r="D151">
@@ -6086,7 +6089,7 @@
         <v>654</v>
       </c>
       <c r="C152" t="str">
-        <f t="shared" si="7"/>
+        <f>A152&amp;" "&amp;B152</f>
         <v>Howard  Merryman (deceased)</v>
       </c>
       <c r="D152">
@@ -6107,7 +6110,7 @@
         <v>655</v>
       </c>
       <c r="C153" t="str">
-        <f t="shared" si="7"/>
+        <f>A153&amp;" "&amp;B153</f>
         <v>Ron  Messerly (deceased)</v>
       </c>
       <c r="D153">
@@ -6128,7 +6131,7 @@
         <v>826</v>
       </c>
       <c r="C154" t="str">
-        <f t="shared" si="7"/>
+        <f>A154&amp;" "&amp;B154</f>
         <v>Bob  Michael (deceased)</v>
       </c>
       <c r="D154">
@@ -6149,7 +6152,7 @@
         <v>698</v>
       </c>
       <c r="C155" t="str">
-        <f t="shared" si="7"/>
+        <f>A155&amp;" "&amp;B155</f>
         <v>Bobby Michaelson</v>
       </c>
       <c r="D155">
@@ -6167,7 +6170,7 @@
         <v>229</v>
       </c>
       <c r="C156" t="str">
-        <f t="shared" si="7"/>
+        <f>A156&amp;" "&amp;B156</f>
         <v xml:space="preserve">John  Millis </v>
       </c>
       <c r="D156">
@@ -6188,7 +6191,7 @@
         <v>608</v>
       </c>
       <c r="C157" t="str">
-        <f t="shared" si="7"/>
+        <f>A157&amp;" "&amp;B157</f>
         <v>Jack  Minder</v>
       </c>
       <c r="D157">
@@ -6206,7 +6209,7 @@
         <v>232</v>
       </c>
       <c r="C158" t="str">
-        <f t="shared" si="7"/>
+        <f>A158&amp;" "&amp;B158</f>
         <v xml:space="preserve">Dean  Minor </v>
       </c>
       <c r="D158">
@@ -6227,7 +6230,7 @@
         <v>522</v>
       </c>
       <c r="C159" t="str">
-        <f t="shared" si="7"/>
+        <f>A159&amp;" "&amp;B159</f>
         <v>Don  Moes</v>
       </c>
       <c r="D159">
@@ -6245,7 +6248,7 @@
         <v>694</v>
       </c>
       <c r="C160" t="str">
-        <f t="shared" si="7"/>
+        <f>A160&amp;" "&amp;B160</f>
         <v>Gordon Mollman (deceased)</v>
       </c>
       <c r="D160">
@@ -6266,7 +6269,7 @@
         <v>237</v>
       </c>
       <c r="C161" t="str">
-        <f t="shared" si="7"/>
+        <f>A161&amp;" "&amp;B161</f>
         <v xml:space="preserve">Leo  Morris </v>
       </c>
       <c r="D161">
@@ -6287,7 +6290,7 @@
         <v>682</v>
       </c>
       <c r="C162" t="str">
-        <f t="shared" si="7"/>
+        <f>A162&amp;" "&amp;B162</f>
         <v>John Muench</v>
       </c>
       <c r="D162">
@@ -6314,7 +6317,7 @@
         <v>240</v>
       </c>
       <c r="C163" t="str">
-        <f t="shared" si="7"/>
+        <f>A163&amp;" "&amp;B163</f>
         <v xml:space="preserve">Howard  Mullica </v>
       </c>
       <c r="D163">
@@ -6335,7 +6338,7 @@
         <v>523</v>
       </c>
       <c r="C164" t="str">
-        <f t="shared" si="7"/>
+        <f>A164&amp;" "&amp;B164</f>
         <v>Duane Murray</v>
       </c>
       <c r="D164">
@@ -6362,7 +6365,7 @@
         <v>701</v>
       </c>
       <c r="C165" t="str">
-        <f t="shared" si="7"/>
+        <f>A165&amp;" "&amp;B165</f>
         <v>Tony Nelson</v>
       </c>
       <c r="D165">
@@ -6380,7 +6383,7 @@
         <v>466</v>
       </c>
       <c r="C166" t="str">
-        <f t="shared" ref="C166:C200" si="8">A166&amp;" "&amp;B166</f>
+        <f>A166&amp;" "&amp;B166</f>
         <v>Stan Nelson (deceased)</v>
       </c>
       <c r="D166">
@@ -6398,7 +6401,7 @@
         <v>466</v>
       </c>
       <c r="C167" t="str">
-        <f t="shared" si="8"/>
+        <f>A167&amp;" "&amp;B167</f>
         <v>Russell  Nelson (deceased)</v>
       </c>
       <c r="D167">
@@ -6419,7 +6422,7 @@
         <v>573</v>
       </c>
       <c r="C168" t="str">
-        <f t="shared" si="8"/>
+        <f>A168&amp;" "&amp;B168</f>
         <v>Gus  Nemitz</v>
       </c>
       <c r="D168">
@@ -6437,7 +6440,7 @@
         <v>245</v>
       </c>
       <c r="C169" t="str">
-        <f t="shared" si="8"/>
+        <f>A169&amp;" "&amp;B169</f>
         <v xml:space="preserve">Junior  Nichols </v>
       </c>
       <c r="D169">
@@ -6458,7 +6461,7 @@
         <v>248</v>
       </c>
       <c r="C170" t="str">
-        <f t="shared" si="8"/>
+        <f>A170&amp;" "&amp;B170</f>
         <v xml:space="preserve">Steve  Nielsen </v>
       </c>
       <c r="D170">
@@ -6479,7 +6482,7 @@
         <v>709</v>
       </c>
       <c r="C171" t="str">
-        <f t="shared" si="8"/>
+        <f>A171&amp;" "&amp;B171</f>
         <v>Leo Nikkel (deceased)</v>
       </c>
       <c r="D171">
@@ -6503,7 +6506,7 @@
         <v>695</v>
       </c>
       <c r="C172" t="str">
-        <f t="shared" si="8"/>
+        <f>A172&amp;" "&amp;B172</f>
         <v>Ray  Nissly (deceased)</v>
       </c>
       <c r="D172">
@@ -6524,7 +6527,7 @@
         <v>450</v>
       </c>
       <c r="C173" t="str">
-        <f t="shared" si="8"/>
+        <f>A173&amp;" "&amp;B173</f>
         <v>Jack  North (deceased)</v>
       </c>
       <c r="D173">
@@ -6542,7 +6545,7 @@
         <v>541</v>
       </c>
       <c r="C174" t="str">
-        <f t="shared" si="8"/>
+        <f>A174&amp;" "&amp;B174</f>
         <v>Shawn O'Brien</v>
       </c>
       <c r="D174">
@@ -6560,7 +6563,7 @@
         <v>421</v>
       </c>
       <c r="C175" t="str">
-        <f t="shared" ref="C175" si="9">A175&amp;" "&amp;B175</f>
+        <f>A175&amp;" "&amp;B175</f>
         <v>Jack  Ogden (deceased)</v>
       </c>
       <c r="D175">
@@ -6578,7 +6581,7 @@
         <v>832</v>
       </c>
       <c r="C176" t="str">
-        <f t="shared" si="8"/>
+        <f>A176&amp;" "&amp;B176</f>
         <v>John "JR" Ogden</v>
       </c>
       <c r="D176">
@@ -6596,7 +6599,7 @@
         <v>763</v>
       </c>
       <c r="C177" t="str">
-        <f t="shared" si="8"/>
+        <f>A177&amp;" "&amp;B177</f>
         <v>Michael Olson</v>
       </c>
       <c r="D177">
@@ -6615,11 +6618,11 @@
         <v>256</v>
       </c>
       <c r="B178" t="s">
-        <v>254</v>
+        <v>838</v>
       </c>
       <c r="C178" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">Gene  Olson </v>
+        <f>A178&amp;" "&amp;B178</f>
+        <v>Gene  Olson  (deceased)</v>
       </c>
       <c r="D178">
         <v>1997</v>
@@ -6639,7 +6642,7 @@
         <v>254</v>
       </c>
       <c r="C179" t="str">
-        <f t="shared" si="8"/>
+        <f>A179&amp;" "&amp;B179</f>
         <v xml:space="preserve">Tim Olson </v>
       </c>
       <c r="D179">
@@ -6660,7 +6663,7 @@
         <v>757</v>
       </c>
       <c r="C180" t="str">
-        <f t="shared" si="8"/>
+        <f>A180&amp;" "&amp;B180</f>
         <v>Dean  Olson (deceased)</v>
       </c>
       <c r="D180">
@@ -6681,7 +6684,7 @@
         <v>745</v>
       </c>
       <c r="C181" t="str">
-        <f t="shared" si="8"/>
+        <f>A181&amp;" "&amp;B181</f>
         <v>Tom Owen</v>
       </c>
       <c r="D181">
@@ -6700,7 +6703,7 @@
         <v>825</v>
       </c>
       <c r="C182" t="str">
-        <f t="shared" si="8"/>
+        <f>A182&amp;" "&amp;B182</f>
         <v>Kurt Packingham (deceased)</v>
       </c>
       <c r="D182">
@@ -6724,7 +6727,7 @@
         <v>833</v>
       </c>
       <c r="C183" t="str">
-        <f t="shared" ref="C183" si="10">A183&amp;" "&amp;B183</f>
+        <f>A183&amp;" "&amp;B183</f>
         <v>Matt Palazzo</v>
       </c>
       <c r="D183">
@@ -6742,7 +6745,7 @@
         <v>385</v>
       </c>
       <c r="C184" t="str">
-        <f t="shared" si="8"/>
+        <f>A184&amp;" "&amp;B184</f>
         <v>Mike Palleson (deceased)</v>
       </c>
       <c r="D184">
@@ -6760,7 +6763,7 @@
         <v>774</v>
       </c>
       <c r="C185" t="str">
-        <f t="shared" si="8"/>
+        <f>A185&amp;" "&amp;B185</f>
         <v>Mark Paulsen</v>
       </c>
       <c r="D185">
@@ -6782,7 +6785,7 @@
         <v>810</v>
       </c>
       <c r="C186" t="str">
-        <f t="shared" si="8"/>
+        <f>A186&amp;" "&amp;B186</f>
         <v>Steve Peot</v>
       </c>
       <c r="D186">
@@ -6803,7 +6806,7 @@
         <v>687</v>
       </c>
       <c r="C187" t="str">
-        <f t="shared" si="8"/>
+        <f>A187&amp;" "&amp;B187</f>
         <v>Bill  Peters (deceased)</v>
       </c>
       <c r="D187">
@@ -6824,7 +6827,7 @@
         <v>748</v>
       </c>
       <c r="C188" t="str">
-        <f t="shared" si="8"/>
+        <f>A188&amp;" "&amp;B188</f>
         <v>Scott Petersen</v>
       </c>
       <c r="D188">
@@ -6843,7 +6846,7 @@
         <v>260</v>
       </c>
       <c r="C189" t="str">
-        <f t="shared" si="8"/>
+        <f>A189&amp;" "&amp;B189</f>
         <v>Tom Peterson</v>
       </c>
       <c r="D189">
@@ -6879,7 +6882,7 @@
         <v>786</v>
       </c>
       <c r="C190" t="str">
-        <f t="shared" si="8"/>
+        <f>A190&amp;" "&amp;B190</f>
         <v>George Peterson (deceased)</v>
       </c>
       <c r="D190">
@@ -6898,7 +6901,7 @@
         <v>503</v>
       </c>
       <c r="C191" t="str">
-        <f t="shared" si="8"/>
+        <f>A191&amp;" "&amp;B191</f>
         <v>Byron Peyton</v>
       </c>
       <c r="D191">
@@ -6926,7 +6929,7 @@
         <v>503</v>
       </c>
       <c r="C192" t="str">
-        <f t="shared" ref="C192" si="11">A192&amp;" "&amp;B192</f>
+        <f>A192&amp;" "&amp;B192</f>
         <v>Doug Peyton</v>
       </c>
       <c r="D192">
@@ -6946,7 +6949,7 @@
         <v>819</v>
       </c>
       <c r="C193" t="str">
-        <f t="shared" si="8"/>
+        <f>A193&amp;" "&amp;B193</f>
         <v>Steve "Seve" Phillips</v>
       </c>
       <c r="D193">
@@ -6966,7 +6969,7 @@
         <v>410</v>
       </c>
       <c r="C194" t="str">
-        <f t="shared" si="8"/>
+        <f>A194&amp;" "&amp;B194</f>
         <v>Walter Plude (deceased)</v>
       </c>
       <c r="D194">
@@ -6985,7 +6988,7 @@
         <v>267</v>
       </c>
       <c r="C195" t="str">
-        <f t="shared" si="8"/>
+        <f>A195&amp;" "&amp;B195</f>
         <v xml:space="preserve">Jerry  Ralfs </v>
       </c>
       <c r="D195">
@@ -7006,7 +7009,7 @@
         <v>271</v>
       </c>
       <c r="C196" t="str">
-        <f t="shared" si="8"/>
+        <f>A196&amp;" "&amp;B196</f>
         <v>Al Rausch</v>
       </c>
       <c r="D196">
@@ -7030,7 +7033,7 @@
         <v>275</v>
       </c>
       <c r="C197" t="str">
-        <f t="shared" si="8"/>
+        <f>A197&amp;" "&amp;B197</f>
         <v xml:space="preserve">Bill  Reames </v>
       </c>
       <c r="D197">
@@ -7051,7 +7054,7 @@
         <v>426</v>
       </c>
       <c r="C198" t="str">
-        <f t="shared" si="8"/>
+        <f>A198&amp;" "&amp;B198</f>
         <v>Paul Reberry (deceased)</v>
       </c>
       <c r="D198">
@@ -7069,7 +7072,7 @@
         <v>638</v>
       </c>
       <c r="C199" t="str">
-        <f t="shared" si="8"/>
+        <f>A199&amp;" "&amp;B199</f>
         <v>Alan Rebling</v>
       </c>
       <c r="D199">
@@ -7096,7 +7099,7 @@
         <v>279</v>
       </c>
       <c r="C200" t="str">
-        <f t="shared" si="8"/>
+        <f>A200&amp;" "&amp;B200</f>
         <v xml:space="preserve">Bubba  Reid </v>
       </c>
       <c r="D200">
@@ -7117,7 +7120,7 @@
         <v>279</v>
       </c>
       <c r="C201" t="str">
-        <f t="shared" ref="C201:C233" si="12">A201&amp;" "&amp;B201</f>
+        <f>A201&amp;" "&amp;B201</f>
         <v xml:space="preserve">Clyde Reid </v>
       </c>
       <c r="D201">
@@ -7135,7 +7138,7 @@
         <v>706</v>
       </c>
       <c r="C202" t="str">
-        <f t="shared" si="12"/>
+        <f>A202&amp;" "&amp;B202</f>
         <v>Maurice  Reid (deceased)</v>
       </c>
       <c r="D202">
@@ -7159,7 +7162,7 @@
         <v>712</v>
       </c>
       <c r="C203" t="str">
-        <f t="shared" si="12"/>
+        <f>A203&amp;" "&amp;B203</f>
         <v>Cliff  Rice (deceased)</v>
       </c>
       <c r="D203">
@@ -7180,7 +7183,7 @@
         <v>396</v>
       </c>
       <c r="C204" t="str">
-        <f t="shared" si="12"/>
+        <f>A204&amp;" "&amp;B204</f>
         <v>John "Smitty" Ringus (deceased)</v>
       </c>
       <c r="D204">
@@ -7198,7 +7201,7 @@
         <v>288</v>
       </c>
       <c r="C205" t="str">
-        <f t="shared" si="12"/>
+        <f>A205&amp;" "&amp;B205</f>
         <v>Randy Ripperger</v>
       </c>
       <c r="D205">
@@ -7228,7 +7231,7 @@
         <v>661</v>
       </c>
       <c r="C206" t="str">
-        <f t="shared" si="12"/>
+        <f>A206&amp;" "&amp;B206</f>
         <v>Vic  Rodenberg (deceased)</v>
       </c>
       <c r="D206">
@@ -7249,7 +7252,7 @@
         <v>295</v>
       </c>
       <c r="C207" t="str">
-        <f t="shared" si="12"/>
+        <f>A207&amp;" "&amp;B207</f>
         <v xml:space="preserve">Dale  Root </v>
       </c>
       <c r="D207">
@@ -7270,7 +7273,7 @@
         <v>433</v>
       </c>
       <c r="C208" t="str">
-        <f t="shared" si="12"/>
+        <f>A208&amp;" "&amp;B208</f>
         <v>Harold Rouse (deceased)</v>
       </c>
       <c r="D208">
@@ -7288,7 +7291,7 @@
         <v>690</v>
       </c>
       <c r="C209" t="str">
-        <f t="shared" si="12"/>
+        <f>A209&amp;" "&amp;B209</f>
         <v>Roger  Ruhs (deceased)</v>
       </c>
       <c r="D209">
@@ -7312,7 +7315,7 @@
         <v>299</v>
       </c>
       <c r="C210" t="str">
-        <f t="shared" si="12"/>
+        <f>A210&amp;" "&amp;B210</f>
         <v xml:space="preserve">Emory  Sample </v>
       </c>
       <c r="D210">
@@ -7333,7 +7336,7 @@
         <v>677</v>
       </c>
       <c r="C211" t="str">
-        <f t="shared" si="12"/>
+        <f>A211&amp;" "&amp;B211</f>
         <v>Pete Sandman</v>
       </c>
       <c r="D211">
@@ -7360,7 +7363,7 @@
         <v>301</v>
       </c>
       <c r="C212" t="str">
-        <f t="shared" si="12"/>
+        <f>A212&amp;" "&amp;B212</f>
         <v>Jerry  Sands</v>
       </c>
       <c r="D212">
@@ -7381,7 +7384,7 @@
         <v>304</v>
       </c>
       <c r="C213" t="str">
-        <f t="shared" si="12"/>
+        <f>A213&amp;" "&amp;B213</f>
         <v xml:space="preserve">Bob  Savage </v>
       </c>
       <c r="D213">
@@ -7402,7 +7405,7 @@
         <v>750</v>
       </c>
       <c r="C214" t="str">
-        <f t="shared" si="12"/>
+        <f>A214&amp;" "&amp;B214</f>
         <v>Jerry  Schneekloth</v>
       </c>
       <c r="D214">
@@ -7430,7 +7433,7 @@
         <v>449</v>
       </c>
       <c r="C215" t="str">
-        <f t="shared" si="12"/>
+        <f>A215&amp;" "&amp;B215</f>
         <v>Clarence Schukel (deceased)</v>
       </c>
       <c r="D215">
@@ -7448,7 +7451,7 @@
         <v>308</v>
       </c>
       <c r="C216" t="str">
-        <f t="shared" si="12"/>
+        <f>A216&amp;" "&amp;B216</f>
         <v xml:space="preserve">Hans  Sell  </v>
       </c>
       <c r="D216">
@@ -7469,7 +7472,7 @@
         <v>521</v>
       </c>
       <c r="C217" t="str">
-        <f t="shared" si="12"/>
+        <f>A217&amp;" "&amp;B217</f>
         <v>Ed Sharp</v>
       </c>
       <c r="D217">
@@ -7487,7 +7490,7 @@
         <v>311</v>
       </c>
       <c r="C218" t="str">
-        <f t="shared" si="12"/>
+        <f>A218&amp;" "&amp;B218</f>
         <v xml:space="preserve">Bob  Sheldon </v>
       </c>
       <c r="D218">
@@ -7508,7 +7511,7 @@
         <v>313</v>
       </c>
       <c r="C219" t="str">
-        <f t="shared" si="12"/>
+        <f>A219&amp;" "&amp;B219</f>
         <v xml:space="preserve">John  Shuey </v>
       </c>
       <c r="D219">
@@ -7529,7 +7532,7 @@
         <v>567</v>
       </c>
       <c r="C220" t="str">
-        <f t="shared" si="12"/>
+        <f>A220&amp;" "&amp;B220</f>
         <v>Steve Shultz (deceased)</v>
       </c>
       <c r="D220">
@@ -7547,7 +7550,7 @@
         <v>317</v>
       </c>
       <c r="C221" t="str">
-        <f t="shared" si="12"/>
+        <f>A221&amp;" "&amp;B221</f>
         <v>Stan Siecel</v>
       </c>
       <c r="D221">
@@ -7565,7 +7568,7 @@
         <v>792</v>
       </c>
       <c r="C222" t="str">
-        <f t="shared" si="12"/>
+        <f>A222&amp;" "&amp;B222</f>
         <v>Joe Simoni</v>
       </c>
       <c r="D222">
@@ -7583,7 +7586,7 @@
         <v>319</v>
       </c>
       <c r="C223" t="str">
-        <f t="shared" si="12"/>
+        <f>A223&amp;" "&amp;B223</f>
         <v xml:space="preserve">Dallas  Slagle </v>
       </c>
       <c r="D223">
@@ -7604,7 +7607,7 @@
         <v>827</v>
       </c>
       <c r="C224" t="str">
-        <f t="shared" si="12"/>
+        <f>A224&amp;" "&amp;B224</f>
         <v>Joe  A. Smith (deceased 7-23-23)</v>
       </c>
       <c r="D224">
@@ -7628,7 +7631,7 @@
         <v>322</v>
       </c>
       <c r="C225" t="str">
-        <f t="shared" si="12"/>
+        <f>A225&amp;" "&amp;B225</f>
         <v xml:space="preserve">Dick  Smith </v>
       </c>
       <c r="D225">
@@ -7649,7 +7652,7 @@
         <v>795</v>
       </c>
       <c r="C226" t="str">
-        <f t="shared" si="12"/>
+        <f>A226&amp;" "&amp;B226</f>
         <v>Rich  Smith  (deceased 2021)</v>
       </c>
       <c r="D226">
@@ -7670,7 +7673,7 @@
         <v>322</v>
       </c>
       <c r="C227" t="str">
-        <f t="shared" ref="C227" si="13">A227&amp;" "&amp;B227</f>
+        <f>A227&amp;" "&amp;B227</f>
         <v xml:space="preserve">Scott Smith </v>
       </c>
       <c r="D227">
@@ -7688,7 +7691,7 @@
         <v>724</v>
       </c>
       <c r="C228" t="str">
-        <f t="shared" si="12"/>
+        <f>A228&amp;" "&amp;B228</f>
         <v>Allen Sobieski</v>
       </c>
       <c r="D228">
@@ -7706,7 +7709,7 @@
         <v>699</v>
       </c>
       <c r="C229" t="str">
-        <f t="shared" si="12"/>
+        <f>A229&amp;" "&amp;B229</f>
         <v>Jim Sokolic</v>
       </c>
       <c r="D229">
@@ -7724,7 +7727,7 @@
         <v>425</v>
       </c>
       <c r="C230" t="str">
-        <f t="shared" si="12"/>
+        <f>A230&amp;" "&amp;B230</f>
         <v>Maurice  Soloman (deceased)</v>
       </c>
       <c r="D230">
@@ -7742,7 +7745,7 @@
         <v>609</v>
       </c>
       <c r="C231" t="str">
-        <f t="shared" si="12"/>
+        <f>A231&amp;" "&amp;B231</f>
         <v>Jim Sovereign</v>
       </c>
       <c r="D231">
@@ -7760,7 +7763,7 @@
         <v>326</v>
       </c>
       <c r="C232" t="str">
-        <f t="shared" si="12"/>
+        <f>A232&amp;" "&amp;B232</f>
         <v xml:space="preserve">Tom  Stahle </v>
       </c>
       <c r="D232">
@@ -7781,7 +7784,7 @@
         <v>329</v>
       </c>
       <c r="C233" t="str">
-        <f t="shared" si="12"/>
+        <f>A233&amp;" "&amp;B233</f>
         <v xml:space="preserve">Mel  Stark </v>
       </c>
       <c r="D233">
@@ -7802,7 +7805,7 @@
         <v>755</v>
       </c>
       <c r="C234" t="str">
-        <f t="shared" ref="C234:C268" si="14">A234&amp;" "&amp;B234</f>
+        <f>A234&amp;" "&amp;B234</f>
         <v>Mike Stickney</v>
       </c>
       <c r="D234">
@@ -7821,7 +7824,7 @@
         <v>331</v>
       </c>
       <c r="C235" t="str">
-        <f t="shared" si="14"/>
+        <f>A235&amp;" "&amp;B235</f>
         <v xml:space="preserve">Tom  Stokesbary </v>
       </c>
       <c r="D235">
@@ -7845,7 +7848,7 @@
         <v>464</v>
       </c>
       <c r="C236" t="str">
-        <f t="shared" si="14"/>
+        <f>A236&amp;" "&amp;B236</f>
         <v>Joe Straub (deceased)</v>
       </c>
       <c r="D236">
@@ -7863,7 +7866,7 @@
         <v>456</v>
       </c>
       <c r="C237" t="str">
-        <f t="shared" si="14"/>
+        <f>A237&amp;" "&amp;B237</f>
         <v>John "Skinny" Straw (deceased)</v>
       </c>
       <c r="D237">
@@ -7881,7 +7884,7 @@
         <v>332</v>
       </c>
       <c r="C238" t="str">
-        <f t="shared" ref="C238" si="15">A238&amp;" "&amp;B238</f>
+        <f>A238&amp;" "&amp;B238</f>
         <v xml:space="preserve">Bob  Sturges </v>
       </c>
       <c r="D238">
@@ -7902,7 +7905,7 @@
         <v>837</v>
       </c>
       <c r="C239" t="str">
-        <f t="shared" si="14"/>
+        <f>A239&amp;" "&amp;B239</f>
         <v>Charles Stufflebeem, Sr.</v>
       </c>
       <c r="D239">
@@ -7920,7 +7923,7 @@
         <v>336</v>
       </c>
       <c r="C240" t="str">
-        <f t="shared" ref="C240" si="16">A240&amp;" "&amp;B240</f>
+        <f>A240&amp;" "&amp;B240</f>
         <v xml:space="preserve">Pat  Sullivan </v>
       </c>
       <c r="D240">
@@ -7941,7 +7944,7 @@
         <v>834</v>
       </c>
       <c r="C241" t="str">
-        <f t="shared" si="14"/>
+        <f>A241&amp;" "&amp;B241</f>
         <v>Larry Svoboda</v>
       </c>
       <c r="D241">
@@ -7959,7 +7962,7 @@
         <v>759</v>
       </c>
       <c r="C242" t="str">
-        <f t="shared" si="14"/>
+        <f>A242&amp;" "&amp;B242</f>
         <v>David Temple (deceased)</v>
       </c>
       <c r="D242">
@@ -7989,7 +7992,7 @@
         <v>760</v>
       </c>
       <c r="C243" t="str">
-        <f t="shared" si="14"/>
+        <f>A243&amp;" "&amp;B243</f>
         <v>Max Tevebaugh (deceased)</v>
       </c>
       <c r="D243">
@@ -8007,7 +8010,7 @@
         <v>387</v>
       </c>
       <c r="C244" t="str">
-        <f t="shared" si="14"/>
+        <f>A244&amp;" "&amp;B244</f>
         <v>Phil Thomas (deceased)</v>
       </c>
       <c r="D244">
@@ -8025,7 +8028,7 @@
         <v>387</v>
       </c>
       <c r="C245" t="str">
-        <f t="shared" si="14"/>
+        <f>A245&amp;" "&amp;B245</f>
         <v>Ray  Thomas (deceased)</v>
       </c>
       <c r="D245">
@@ -8043,7 +8046,7 @@
         <v>488</v>
       </c>
       <c r="C246" t="str">
-        <f t="shared" si="14"/>
+        <f>A246&amp;" "&amp;B246</f>
         <v>Bob Timmons</v>
       </c>
       <c r="D246">
@@ -8067,7 +8070,7 @@
         <v>536</v>
       </c>
       <c r="C247" t="str">
-        <f t="shared" si="14"/>
+        <f>A247&amp;" "&amp;B247</f>
         <v>Mike Tranel</v>
       </c>
       <c r="D247">
@@ -8091,7 +8094,7 @@
         <v>455</v>
       </c>
       <c r="C248" t="str">
-        <f t="shared" si="14"/>
+        <f>A248&amp;" "&amp;B248</f>
         <v>Dick  Tratchel (deceased)</v>
       </c>
       <c r="D248">
@@ -8109,7 +8112,7 @@
         <v>405</v>
       </c>
       <c r="C249" t="str">
-        <f t="shared" si="14"/>
+        <f>A249&amp;" "&amp;B249</f>
         <v>Dick  Triggs (deceased)</v>
       </c>
       <c r="D249">
@@ -8127,7 +8130,7 @@
         <v>343</v>
       </c>
       <c r="C250" t="str">
-        <f t="shared" si="14"/>
+        <f>A250&amp;" "&amp;B250</f>
         <v xml:space="preserve">Gene  Turner </v>
       </c>
       <c r="D250">
@@ -8148,7 +8151,7 @@
         <v>630</v>
       </c>
       <c r="C251" t="str">
-        <f t="shared" si="14"/>
+        <f>A251&amp;" "&amp;B251</f>
         <v>Todd Twachtmann</v>
       </c>
       <c r="D251">
@@ -8166,7 +8169,7 @@
         <v>424</v>
       </c>
       <c r="C252" t="str">
-        <f t="shared" si="14"/>
+        <f>A252&amp;" "&amp;B252</f>
         <v>Leon "Rookie" Uknes (deceased)</v>
       </c>
       <c r="D252">
@@ -8184,7 +8187,7 @@
         <v>345</v>
       </c>
       <c r="C253" t="str">
-        <f t="shared" si="14"/>
+        <f>A253&amp;" "&amp;B253</f>
         <v xml:space="preserve">Al Van Dyke </v>
       </c>
       <c r="D253">
@@ -8205,7 +8208,7 @@
         <v>440</v>
       </c>
       <c r="C254" t="str">
-        <f t="shared" si="14"/>
+        <f>A254&amp;" "&amp;B254</f>
         <v>Kelly Van Eee (deceased)</v>
       </c>
       <c r="D254">
@@ -8223,7 +8226,7 @@
         <v>776</v>
       </c>
       <c r="C255" t="str">
-        <f t="shared" si="14"/>
+        <f>A255&amp;" "&amp;B255</f>
         <v>Steve Van Ginkel</v>
       </c>
       <c r="D255">
@@ -8243,7 +8246,7 @@
         <v>454</v>
       </c>
       <c r="C256" t="str">
-        <f t="shared" si="14"/>
+        <f>A256&amp;" "&amp;B256</f>
         <v>Bobby Vandever (deceased)</v>
       </c>
       <c r="D256">
@@ -8261,7 +8264,7 @@
         <v>528</v>
       </c>
       <c r="C257" t="str">
-        <f t="shared" si="14"/>
+        <f>A257&amp;" "&amp;B257</f>
         <v>Clint Vonk</v>
       </c>
       <c r="D257">
@@ -8279,7 +8282,7 @@
         <v>622</v>
       </c>
       <c r="C258" t="str">
-        <f t="shared" si="14"/>
+        <f>A258&amp;" "&amp;B258</f>
         <v>Dan Wakefield</v>
       </c>
       <c r="D258">
@@ -8297,7 +8300,7 @@
         <v>517</v>
       </c>
       <c r="C259" t="str">
-        <f t="shared" si="14"/>
+        <f>A259&amp;" "&amp;B259</f>
         <v>Duane "Tuff" Walker (deceased)</v>
       </c>
       <c r="D259">
@@ -8315,7 +8318,7 @@
         <v>348</v>
       </c>
       <c r="C260" t="str">
-        <f t="shared" si="14"/>
+        <f>A260&amp;" "&amp;B260</f>
         <v xml:space="preserve">Bill  Wall </v>
       </c>
       <c r="D260">
@@ -8336,7 +8339,7 @@
         <v>394</v>
       </c>
       <c r="C261" t="str">
-        <f t="shared" si="14"/>
+        <f>A261&amp;" "&amp;B261</f>
         <v>Bill  Weatley (deceased)</v>
       </c>
       <c r="D261">
@@ -8354,7 +8357,7 @@
         <v>807</v>
       </c>
       <c r="C262" t="str">
-        <f t="shared" ref="C262" si="17">A262&amp;" "&amp;B262</f>
+        <f>A262&amp;" "&amp;B262</f>
         <v>Brad Wedeking</v>
       </c>
       <c r="D262">
@@ -8375,7 +8378,7 @@
         <v>807</v>
       </c>
       <c r="C263" t="str">
-        <f t="shared" si="14"/>
+        <f>A263&amp;" "&amp;B263</f>
         <v>Joe Wedeking</v>
       </c>
       <c r="D263">
@@ -8396,7 +8399,7 @@
         <v>352</v>
       </c>
       <c r="C264" t="str">
-        <f t="shared" si="14"/>
+        <f>A264&amp;" "&amp;B264</f>
         <v>Leroy Wegmann</v>
       </c>
       <c r="D264">
@@ -8429,7 +8432,7 @@
         <v>358</v>
       </c>
       <c r="C265" t="str">
-        <f t="shared" si="14"/>
+        <f>A265&amp;" "&amp;B265</f>
         <v>Chuck Welker</v>
       </c>
       <c r="D265">
@@ -8453,7 +8456,7 @@
         <v>727</v>
       </c>
       <c r="C266" t="str">
-        <f t="shared" si="14"/>
+        <f>A266&amp;" "&amp;B266</f>
         <v>Mike White</v>
       </c>
       <c r="D266">
@@ -8471,7 +8474,7 @@
         <v>463</v>
       </c>
       <c r="C267" t="str">
-        <f t="shared" si="14"/>
+        <f>A267&amp;" "&amp;B267</f>
         <v>Father Bernard White (deceased)</v>
       </c>
       <c r="D267">
@@ -8489,7 +8492,7 @@
         <v>463</v>
       </c>
       <c r="C268" t="str">
-        <f t="shared" si="14"/>
+        <f>A268&amp;" "&amp;B268</f>
         <v>Ed  White (deceased)</v>
       </c>
       <c r="D268">
@@ -8510,7 +8513,7 @@
         <v>664</v>
       </c>
       <c r="C269" t="str">
-        <f t="shared" ref="C269:C277" si="18">A269&amp;" "&amp;B269</f>
+        <f>A269&amp;" "&amp;B269</f>
         <v>Dean Whitebreast</v>
       </c>
       <c r="D269">
@@ -8537,7 +8540,7 @@
         <v>365</v>
       </c>
       <c r="C270" t="str">
-        <f t="shared" si="18"/>
+        <f>A270&amp;" "&amp;B270</f>
         <v xml:space="preserve">Phil Wilkinson (deceased) </v>
       </c>
       <c r="D270">
@@ -8555,7 +8558,7 @@
         <v>708</v>
       </c>
       <c r="C271" t="str">
-        <f t="shared" si="18"/>
+        <f>A271&amp;" "&amp;B271</f>
         <v>Dean Williams (deceased)</v>
       </c>
       <c r="D271">
@@ -8579,7 +8582,7 @@
         <v>756</v>
       </c>
       <c r="C272" t="str">
-        <f t="shared" si="18"/>
+        <f>A272&amp;" "&amp;B272</f>
         <v>Stan Wisnieski</v>
       </c>
       <c r="D272">
@@ -8598,7 +8601,7 @@
         <v>430</v>
       </c>
       <c r="C273" t="str">
-        <f t="shared" si="18"/>
+        <f>A273&amp;" "&amp;B273</f>
         <v>Frank Wolf (deceased)</v>
       </c>
       <c r="D273">
@@ -8616,7 +8619,7 @@
         <v>371</v>
       </c>
       <c r="C274" t="str">
-        <f t="shared" si="18"/>
+        <f>A274&amp;" "&amp;B274</f>
         <v>Lou  Yacinich Jr.</v>
       </c>
       <c r="D274">
@@ -8637,7 +8640,7 @@
         <v>538</v>
       </c>
       <c r="C275" t="str">
-        <f t="shared" si="18"/>
+        <f>A275&amp;" "&amp;B275</f>
         <v>Andy Yates</v>
       </c>
       <c r="D275">
@@ -8661,7 +8664,7 @@
         <v>777</v>
       </c>
       <c r="C276" t="str">
-        <f t="shared" si="18"/>
+        <f>A276&amp;" "&amp;B276</f>
         <v>Steve Zediker (deceased)</v>
       </c>
       <c r="D276">
@@ -8691,7 +8694,7 @@
         <v>707</v>
       </c>
       <c r="C277" t="str">
-        <f t="shared" si="18"/>
+        <f>A277&amp;" "&amp;B277</f>
         <v>Darrell  Zunkel (deceased)</v>
       </c>
       <c r="D277">
@@ -8708,7 +8711,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:K268">
+  <sortState ref="A2:K277">
     <sortCondition ref="B2"/>
   </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
